--- a/uririn/streams.xlsx
+++ b/uririn/streams.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="389">
   <si>
     <t>id</t>
   </si>
@@ -35,52 +35,67 @@
     <t>note</t>
   </si>
   <si>
+    <t>description</t>
+  </si>
+  <si>
     <t>【幽李鈴】將在12/20 21:00 初配信啦！💗</t>
   </si>
   <si>
+    <t>【 生物名師】幽李鈴</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=v0BAHTKUHho</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=jd0h91vnRxU</t>
   </si>
   <si>
-    <t>【 生物名師】幽李鈴</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=v0BAHTKUHho</t>
-  </si>
-  <si>
     <t>前導</t>
   </si>
   <si>
+    <t>Twitch</t>
+  </si>
+  <si>
+    <t>1⧸1 115年 生物老師 幽李鈴 第八節</t>
+  </si>
+  <si>
     <t>【一人捉迷藏】恐怖！直播片段丟失！？</t>
   </si>
   <si>
+    <t>【直播取消】感冒休養跟大家請個假！</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=y_6XDNwD-Ks</t>
   </si>
   <si>
-    <t>Twitch</t>
-  </si>
-  <si>
-    <t>1⧸1 115年 生物老師 幽李鈴 第八節</t>
-  </si>
-  <si>
-    <t>【直播取消】感冒休養跟大家請個假！</t>
-  </si>
-  <si>
     <t>https://x.com/U00Vtuber/status/2007422926228689379</t>
   </si>
   <si>
+    <t>X, 直播異動</t>
+  </si>
+  <si>
+    <t>關於今日發生的騷動說明 ft.亞洛赫</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=dUhUhvbywD0</t>
+  </si>
+  <si>
     <t>?????</t>
   </si>
   <si>
-    <t>X, 直播異動</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=BH_IHRUDy_Q</t>
   </si>
   <si>
-    <t>關於今日發生的騷動說明 ft.亞洛赫</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=dUhUhvbywD0</t>
+    <t>直播異動, 連動</t>
+  </si>
+  <si>
+    <t>亞洛赫</t>
+  </si>
+  <si>
+    <t>大便糖速吃...我後悔了</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=v_O4YV6wZtk</t>
   </si>
   <si>
     <t>【神回】直擊！醫院幽靈失蹤事件！</t>
@@ -89,16 +104,13 @@
     <t>https://www.youtube.com/watch?v=d0N94cT487Y</t>
   </si>
   <si>
-    <t>直播異動, 連動</t>
-  </si>
-  <si>
-    <t>亞洛赫</t>
-  </si>
-  <si>
-    <t>大便糖速吃...我後悔了</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=v_O4YV6wZtk</t>
+    <t>QA, 棉花糖</t>
+  </si>
+  <si>
+    <t>【A/S/M/R】嗯哼～♡人家是新手～♡【 NO Sleep /Relax /Whispering】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Vp-lbw9r880</t>
   </si>
   <si>
     <t>【初配信】初次見面！！我是幽李鈴！！</t>
@@ -107,13 +119,13 @@
     <t>https://www.youtube.com/watch?v=Yp2QhS2g0tU</t>
   </si>
   <si>
-    <t>QA, 棉花糖</t>
-  </si>
-  <si>
-    <t>【A/S/M/R】嗯哼～♡人家是新手～♡【 NO Sleep /Relax /Whispering】</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=Vp-lbw9r880</t>
+    <t>ASMR</t>
+  </si>
+  <si>
+    <t>【會員限定】秘密</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KIAUz5M13wo</t>
   </si>
   <si>
     <t>【後日談QA】治安不好的棉花糖很多呢各位</t>
@@ -122,13 +134,13 @@
     <t>https://www.youtube.com/watch?v=kiGVfQRxg5w</t>
   </si>
   <si>
-    <t>ASMR</t>
-  </si>
-  <si>
-    <t>【會員限定】秘密</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=KIAUz5M13wo</t>
+    <t>會限</t>
+  </si>
+  <si>
+    <t>【觀眾CALL IN】 夾子音醫院聯賽</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=HunY1CF0ezs</t>
   </si>
   <si>
     <t>【聖誕初連動】非誠勿擾，今晚能不能配對成功？ft.亞洛赫</t>
@@ -137,13 +149,16 @@
     <t>https://www.youtube.com/watch?v=G9uRcuHZTdM</t>
   </si>
   <si>
-    <t>會限</t>
-  </si>
-  <si>
-    <t>【觀眾CALL IN】 夾子音醫院聯賽</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=HunY1CF0ezs</t>
+    <t>Twitch, 觀眾CALL IN</t>
+  </si>
+  <si>
+    <t>1⧸15 夾子音醫院聯賽  BO5賽事 CALLIN</t>
+  </si>
+  <si>
+    <t>小朋友們！你們最愛的水毒姐姐來囉！(※手超級會動)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=0IHJxtZ_8XE</t>
   </si>
   <si>
     <t>連動</t>
@@ -155,27 +170,27 @@
     <t>https://x.com/U00Vtuber/status/2004465037411602451</t>
   </si>
   <si>
-    <t>Twitch, 觀眾CALL IN</t>
-  </si>
-  <si>
-    <t>1⧸15 夾子音醫院聯賽  BO5賽事 CALLIN</t>
+    <t>手語讓觀眾猜出說甚麼才能宣傳新周邊！？(※禁止說話)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=HMSuYD7A6Pw</t>
   </si>
   <si>
     <t>X, 歌回, Twitch</t>
   </si>
   <si>
-    <t>小朋友們！你們最愛的水毒姐姐來囉！(※手超級會動)</t>
-  </si>
-  <si>
     <t>【收益化慶祝酒雜】今天跟大家喝到掛！！！🥂乾杯！！！</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=0IHJxtZ_8XE</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=3wkLHKQ5Uqo</t>
   </si>
   <si>
+    <t>【觀眾參加型】 賭神降臨</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=GOTc2xgBHq4</t>
+  </si>
+  <si>
     <t>酒雜</t>
   </si>
   <si>
@@ -185,10 +200,16 @@
     <t>https://www.youtube.com/watch?v=3VejobEf1WM</t>
   </si>
   <si>
-    <t>手語讓觀眾猜出說甚麼才能宣傳新周邊！？(※禁止說話)</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=HMSuYD7A6Pw</t>
+    <t>Twitch, 直播異動, 觀眾參加型</t>
+  </si>
+  <si>
+    <t>1⧸22 賭賭賭 嘟嘟嘟</t>
+  </si>
+  <si>
+    <t>讓你想起我是護理師</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Q3ffqBot4OI</t>
   </si>
   <si>
     <t>觀眾CALL IN</t>
@@ -200,37 +221,19 @@
     <t>https://www.youtube.com/watch?v=7LmRg4qqk4M</t>
   </si>
   <si>
-    <t>【觀眾參加型】 賭神降臨</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=GOTc2xgBHq4</t>
+    <t>Twitch, 直播異動</t>
+  </si>
+  <si>
+    <t>1⧸23 讓大家回想起我是護理師</t>
+  </si>
+  <si>
+    <t>【夜間巡房】滿月慶祝酒雜！一起不醉不歸的時間又到了！！</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=_2WOcF57GSI</t>
   </si>
   <si>
     <t>會限, 直播異動</t>
-  </si>
-  <si>
-    <t>Twitch, 直播異動, 觀眾參加型</t>
-  </si>
-  <si>
-    <t>1⧸22 賭賭賭 嘟嘟嘟</t>
-  </si>
-  <si>
-    <t>讓你想起我是護理師</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=Q3ffqBot4OI</t>
-  </si>
-  <si>
-    <t>Twitch, 直播異動</t>
-  </si>
-  <si>
-    <t>1⧸23 讓大家回想起我是護理師</t>
-  </si>
-  <si>
-    <t>【夜間巡房】滿月慶祝酒雜！一起不醉不歸的時間又到了！！</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=_2WOcF57GSI</t>
   </si>
   <si>
     <t>【歌回】唱唱幾首喜歡的新歌</t>
@@ -1482,6 +1485,9 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
@@ -1497,10 +1503,10 @@
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -1514,7 +1520,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>19</v>
@@ -1528,16 +1534,16 @@
         <v>46028.0</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="E4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -1548,13 +1554,13 @@
         <v>46030.0</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -1565,13 +1571,13 @@
         <v>46032.0</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -1582,13 +1588,13 @@
         <v>46035.0</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
@@ -1599,16 +1605,16 @@
         <v>46037.0</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -1619,10 +1625,10 @@
         <v>46039.0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -1633,10 +1639,10 @@
         <v>46042.0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
@@ -1647,16 +1653,16 @@
         <v>46044.0</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="G11" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="12">
@@ -1667,10 +1673,10 @@
         <v>46045.0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>69</v>
@@ -1693,7 +1699,7 @@
         <v>72</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -1704,16 +1710,16 @@
         <v>46048.0</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1724,10 +1730,10 @@
         <v>46052.0</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>19</v>
@@ -1741,19 +1747,19 @@
         <v>46053.0</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17">
@@ -1764,13 +1770,13 @@
         <v>46054.0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18">
@@ -1781,16 +1787,16 @@
         <v>46055.0</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19">
@@ -1801,13 +1807,13 @@
         <v>46056.0</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20">
@@ -1818,16 +1824,16 @@
         <v>46058.0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21">
@@ -1838,10 +1844,10 @@
         <v>46060.0</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>19</v>
@@ -1855,16 +1861,16 @@
         <v>46062.0</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23">
@@ -1875,10 +1881,10 @@
         <v>46065.0</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>19</v>
@@ -1892,10 +1898,10 @@
         <v>46066.0</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25">
@@ -1906,16 +1912,16 @@
         <v>46067.0</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
@@ -1926,10 +1932,10 @@
         <v>46068.0</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>19</v>
@@ -1943,16 +1949,16 @@
         <v>46069.0</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28">
@@ -1963,13 +1969,13 @@
         <v>46069.0</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29">
@@ -1980,10 +1986,10 @@
         <v>46074.0</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>19</v>
@@ -1997,16 +2003,16 @@
         <v>46076.0</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31">
@@ -2017,16 +2023,16 @@
         <v>46077.0</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32">
@@ -2037,13 +2043,13 @@
         <v>46081.0</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33">
@@ -2054,16 +2060,16 @@
         <v>46083.0</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34">
@@ -2074,16 +2080,16 @@
         <v>46086.0</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35">
@@ -2094,16 +2100,16 @@
         <v>46088.0</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36">
@@ -2114,16 +2120,16 @@
         <v>46090.0</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37">
@@ -2134,16 +2140,16 @@
         <v>46094.0</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="38">
@@ -2154,16 +2160,16 @@
         <v>46094.0</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="39">
@@ -2174,13 +2180,13 @@
         <v>46095.0</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40">
@@ -2191,16 +2197,16 @@
         <v>46096.0</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41">
@@ -2211,16 +2217,16 @@
         <v>46097.0</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="42">
@@ -2231,13 +2237,13 @@
         <v>46097.0</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43">
@@ -2248,16 +2254,16 @@
         <v>46098.0</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44">
@@ -2268,16 +2274,16 @@
         <v>46102.0</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="45">
@@ -2288,13 +2294,13 @@
         <v>46103.0</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46">
@@ -2305,10 +2311,10 @@
         <v>46104.0</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>19</v>
@@ -2322,16 +2328,16 @@
         <v>46104.0</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="48">
@@ -2342,10 +2348,10 @@
         <v>46106.0</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="49">
@@ -2356,16 +2362,16 @@
         <v>46108.0</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="50">
@@ -2376,16 +2382,16 @@
         <v>46108.0</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="51">
@@ -2396,16 +2402,16 @@
         <v>46108.0</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="52">
@@ -2416,13 +2422,13 @@
         <v>46109.0</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53">
@@ -2433,10 +2439,10 @@
         <v>46111.0</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>19</v>
@@ -2450,16 +2456,16 @@
         <v>46112.0</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="55">
@@ -2470,16 +2476,16 @@
         <v>46112.0</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56">
@@ -2490,10 +2496,10 @@
         <v>46116.0</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="57">
@@ -2504,13 +2510,13 @@
         <v>46117.0</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58">
@@ -2521,16 +2527,16 @@
         <v>46117.0</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="59">
@@ -2541,16 +2547,16 @@
         <v>46118.0</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="60">
@@ -2561,16 +2567,16 @@
         <v>46118.0</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="61">
@@ -2581,16 +2587,16 @@
         <v>46119.0</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="62">
@@ -2601,19 +2607,19 @@
         <v>46120.0</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63">
@@ -2624,16 +2630,16 @@
         <v>46121.0</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="64">
@@ -2644,13 +2650,13 @@
         <v>46124.0</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="65">
@@ -2661,16 +2667,16 @@
         <v>46125.0</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="66">
@@ -2681,19 +2687,19 @@
         <v>46126.0</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67">
@@ -2704,10 +2710,10 @@
         <v>46127.0</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>19</v>
@@ -2721,10 +2727,10 @@
         <v>46128.0</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>19</v>
@@ -2738,16 +2744,16 @@
         <v>46130.0</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="70">
@@ -2758,16 +2764,16 @@
         <v>46139.0</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="71">
@@ -2778,16 +2784,16 @@
         <v>46140.0</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="72">
@@ -2798,16 +2804,16 @@
         <v>46145.0</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="73">
@@ -2818,16 +2824,16 @@
         <v>46145.0</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="74">
@@ -2838,16 +2844,16 @@
         <v>46155.0</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="75">
@@ -2858,16 +2864,16 @@
         <v>46165.0</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="76">
@@ -2878,16 +2884,16 @@
         <v>46178.0</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77">
@@ -2898,16 +2904,16 @@
         <v>46183.0</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="78">
@@ -2918,13 +2924,13 @@
         <v>46184.0</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="79">
@@ -2935,16 +2941,16 @@
         <v>46187.0</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="80">
@@ -2955,16 +2961,16 @@
         <v>46198.0</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="81">
@@ -2975,16 +2981,16 @@
         <v>46199.0</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="82">
@@ -2995,10 +3001,10 @@
         <v>46215.0</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="83">
@@ -3009,16 +3015,16 @@
         <v>46216.0</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="84">
@@ -3029,13 +3035,13 @@
         <v>46219.0</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="85">
@@ -3046,10 +3052,10 @@
         <v>46221.0</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>19</v>
@@ -3063,16 +3069,16 @@
         <v>46222.0</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="87">
@@ -3083,16 +3089,16 @@
         <v>46224.0</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="88">
@@ -3103,13 +3109,13 @@
         <v>46228.0</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="89">
@@ -3120,10 +3126,10 @@
         <v>46246.0</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="90">
@@ -3134,13 +3140,13 @@
         <v>46246.0</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="91">
@@ -3151,16 +3157,16 @@
         <v>46247.0</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="92">
@@ -3171,13 +3177,13 @@
         <v>46247.0</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="93">
@@ -3188,13 +3194,13 @@
         <v>46248.0</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="94">
@@ -3205,16 +3211,16 @@
         <v>46248.0</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="95">
@@ -3225,13 +3231,13 @@
         <v>46249.0</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="96">
@@ -3242,16 +3248,16 @@
         <v>46249.0</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="97">
@@ -3262,10 +3268,10 @@
         <v>46250.0</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="98">
@@ -3276,16 +3282,16 @@
         <v>46251.0</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="99">
@@ -3296,13 +3302,13 @@
         <v>46252.0</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="100">
@@ -3313,16 +3319,16 @@
         <v>46252.0</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="101">
@@ -3333,13 +3339,13 @@
         <v>46253.0</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102">
@@ -3350,13 +3356,13 @@
         <v>46254.0</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="103">
@@ -3367,13 +3373,13 @@
         <v>46256.0</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="104">
@@ -3384,13 +3390,13 @@
         <v>46258.0</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="105">
@@ -3401,13 +3407,13 @@
         <v>46260.0</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106">
@@ -3418,13 +3424,13 @@
         <v>46260.0</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107">
@@ -3435,13 +3441,13 @@
         <v>46261.0</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="108">
@@ -3452,13 +3458,13 @@
         <v>46263.0</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="109">
@@ -3469,10 +3475,10 @@
         <v>46264.0</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E109" s="1"/>
     </row>
@@ -3484,13 +3490,13 @@
         <v>46266.0</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="111">
@@ -3501,11 +3507,11 @@
         <v>46267.0</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D111" s="1"/>
       <c r="E111" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F111" s="1"/>
     </row>
@@ -3517,16 +3523,16 @@
         <v>46268.0</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="113">
@@ -3537,13 +3543,13 @@
         <v>46269.0</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="114">
@@ -3554,13 +3560,13 @@
         <v>46271.0</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="115">
@@ -3571,13 +3577,13 @@
         <v>46271.0</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="116">
@@ -3588,13 +3594,13 @@
         <v>46274.0</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="117">
@@ -3605,10 +3611,10 @@
         <v>46281.0</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E117" s="5" t="s">
         <v>19</v>
@@ -3623,16 +3629,16 @@
         <v>46282.0</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="119">
@@ -3643,16 +3649,16 @@
         <v>46283.0</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="120">
@@ -3663,16 +3669,16 @@
         <v>46284.0</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="121">
@@ -3683,10 +3689,10 @@
         <v>46285.0</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="122">
@@ -3697,13 +3703,13 @@
         <v>46288.0</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="123">
@@ -3714,16 +3720,16 @@
         <v>46295.0</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="124">
@@ -3734,13 +3740,13 @@
         <v>46295.0</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="125">
@@ -3751,19 +3757,19 @@
         <v>46301.0</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -3934,13 +3940,13 @@
         <v>46000.0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -3951,13 +3957,13 @@
         <v>46011.0</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -3968,13 +3974,13 @@
         <v>46011.0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -3985,16 +3991,16 @@
         <v>46011.0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -4005,10 +4011,10 @@
         <v>46011.0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -4019,13 +4025,13 @@
         <v>46013.0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -4036,16 +4042,16 @@
         <v>46015.0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -4056,13 +4062,13 @@
         <v>46017.0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -4073,13 +4079,13 @@
         <v>46019.0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
@@ -4090,13 +4096,13 @@
         <v>46021.0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12">
@@ -4107,13 +4113,13 @@
         <v>46022.0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
